--- a/engine/arcc_study/ARCC_Valuation_Model_10092026_public.xlsx
+++ b/engine/arcc_study/ARCC_Valuation_Model_10092026_public.xlsx
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="D5" s="14">
-        <f>Assumptions!$B$107</f>
+        <f>Assumptions!$B$109</f>
         <v/>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="D6" s="14">
-        <f>Assumptions!$B$108</f>
+        <f>Assumptions!$B$110</f>
         <v/>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="D7" s="14">
-        <f>Assumptions!$B$109</f>
+        <f>Assumptions!$B$111</f>
         <v/>
       </c>
     </row>
@@ -1263,19 +1263,19 @@
         </is>
       </c>
       <c r="B9" s="14">
+        <f>Assumptions!$B$117</f>
+        <v/>
+      </c>
+      <c r="C9" s="14">
+        <f>Assumptions!$B$116</f>
+        <v/>
+      </c>
+      <c r="D9" s="14">
         <f>Assumptions!$B$115</f>
         <v/>
       </c>
-      <c r="C9" s="14">
-        <f>Assumptions!$B$114</f>
-        <v/>
-      </c>
-      <c r="D9" s="14">
-        <f>Assumptions!$B$113</f>
-        <v/>
-      </c>
       <c r="E9" s="17">
-        <f>D9-Assumptions!$B$132+'Income Statement'!E20+DCF!B8+DCF!B13+DCF!B14-'Income Statement'!E22</f>
+        <f>D9-Assumptions!$B$134+'Income Statement'!E20+DCF!B8+DCF!B13+DCF!B14-'Income Statement'!E22</f>
         <v/>
       </c>
       <c r="F9" s="17">
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="D10" s="17">
-        <f>Assumptions!$B$110+Assumptions!$B$111+Assumptions!$B$112</f>
+        <f>Assumptions!$B$112+Assumptions!$B$113+Assumptions!$B$114</f>
         <v/>
       </c>
       <c r="E10" s="17">
@@ -1333,15 +1333,15 @@
         </is>
       </c>
       <c r="B11" s="32">
+        <f>Assumptions!$B$107</f>
+        <v/>
+      </c>
+      <c r="C11" s="32">
+        <f>Assumptions!$B$106</f>
+        <v/>
+      </c>
+      <c r="D11" s="32">
         <f>Assumptions!$B$105</f>
-        <v/>
-      </c>
-      <c r="C11" s="32">
-        <f>Assumptions!$B$104</f>
-        <v/>
-      </c>
-      <c r="D11" s="32">
-        <f>Assumptions!$B$103</f>
         <v/>
       </c>
       <c r="E11" s="37">
@@ -1372,11 +1372,11 @@
         </is>
       </c>
       <c r="B12" s="14">
-        <f>Assumptions!$B$126</f>
+        <f>Assumptions!$B$128</f>
         <v/>
       </c>
       <c r="C12" s="14">
-        <f>Assumptions!$B$125</f>
+        <f>Assumptions!$B$127</f>
         <v/>
       </c>
       <c r="D12" s="14">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="D14" s="14">
-        <f>Assumptions!$B$106</f>
+        <f>Assumptions!$B$108</f>
         <v/>
       </c>
       <c r="E14" s="17">
@@ -1473,19 +1473,19 @@
         </is>
       </c>
       <c r="B15" s="32">
+        <f>Assumptions!$B$120</f>
+        <v/>
+      </c>
+      <c r="C15" s="32">
+        <f>Assumptions!$B$119</f>
+        <v/>
+      </c>
+      <c r="D15" s="32">
         <f>Assumptions!$B$118</f>
         <v/>
       </c>
-      <c r="C15" s="32">
-        <f>Assumptions!$B$117</f>
-        <v/>
-      </c>
-      <c r="D15" s="32">
-        <f>Assumptions!$B$116</f>
-        <v/>
-      </c>
       <c r="E15" s="37">
-        <f>D15-Assumptions!$B$132+'Income Statement'!E20-'Income Statement'!E22</f>
+        <f>D15-Assumptions!$B$134+'Income Statement'!E20-'Income Statement'!E22</f>
         <v/>
       </c>
       <c r="F15" s="37">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="B21" s="17">
-        <f>Assumptions!$B$103</f>
+        <f>Assumptions!$B$105</f>
         <v/>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="B22" s="17">
-        <f>-Assumptions!$B$106</f>
+        <f>-Assumptions!$B$108</f>
         <v/>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="B24" s="17">
-        <f>Assumptions!$B$116+Assumptions!$B$119</f>
+        <f>Assumptions!$B$118+Assumptions!$B$121</f>
         <v/>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="B6" s="14">
-        <f>Assumptions!$B$83</f>
+        <f>Assumptions!$B$85</f>
         <v/>
       </c>
       <c r="C6" s="14">
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="B9" s="14">
-        <f>-Assumptions!$B$86</f>
+        <f>-Assumptions!$B$88</f>
         <v/>
       </c>
       <c r="C9" s="14">
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="B11" s="14">
-        <f>-Assumptions!$B$132</f>
+        <f>-Assumptions!$B$134</f>
         <v/>
       </c>
       <c r="C11" s="17">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B12" s="14">
-        <f>Assumptions!$B$113</f>
+        <f>Assumptions!$B$115</f>
         <v/>
       </c>
       <c r="C12" s="14">
@@ -2943,102 +2943,102 @@
     </row>
     <row r="6">
       <c r="A6" s="25" t="n">
-        <v>0.2459972623102014</v>
+        <v>0.2496011971672128</v>
       </c>
       <c r="B6" s="21" t="n">
-        <v>80.6116769838753</v>
+        <v>80.28560499094328</v>
       </c>
       <c r="C6" s="21" t="n">
-        <v>80.63863670741269</v>
+        <v>80.31243933560053</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>80.58262713086836</v>
+        <v>80.25669023717182</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>80.42047700800721</v>
+        <v>80.09529420961111</v>
       </c>
       <c r="F6" s="21" t="n">
-        <v>80.11950123398847</v>
+        <v>79.79571815341392</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="25" t="n">
-        <v>0.2609972623102014</v>
+        <v>0.2646011971672128</v>
       </c>
       <c r="B7" s="21" t="n">
-        <v>79.26798525766915</v>
+        <v>78.95036401110004</v>
       </c>
       <c r="C7" s="21" t="n">
-        <v>79.29442846098921</v>
+        <v>78.97668517670607</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>79.23949196958276</v>
+        <v>78.92200222204954</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>79.08044847415357</v>
+        <v>78.76369272636984</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>78.78523908241954</v>
+        <v>78.46984575199836</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="25" t="n">
-        <v>0.2759972623102014</v>
+        <v>0.2796011971672128</v>
       </c>
       <c r="B8" s="21" t="n">
-        <v>77.95900301392194</v>
+        <v>77.64954201226143</v>
       </c>
       <c r="C8" s="21" t="n">
-        <v>77.98494341797416</v>
+        <v>77.67536360358967</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>77.93105150605081</v>
+        <v>77.62171852840966</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>77.77503211296215</v>
+        <v>77.46641373826449</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>77.48543592414525</v>
+        <v>77.17814396333017</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="25" t="n">
-        <v>0.2909972623102015</v>
+        <v>0.2946011971672128</v>
       </c>
       <c r="B9" s="21" t="n">
-        <v>76.6835412283736</v>
+        <v>76.38196252800365</v>
       </c>
       <c r="C9" s="21" t="n">
-        <v>76.7089920786396</v>
+        <v>76.40729767940753</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>76.65611722834244</v>
+        <v>76.35466319671895</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>76.50304227222016</v>
+        <v>76.20228411511789</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>76.21891141503147</v>
+        <v>75.91944490895575</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="25" t="n">
-        <v>0.3059972623102014</v>
+        <v>0.3096011971672128</v>
       </c>
       <c r="B10" s="21" t="n">
-        <v>75.44046208886475</v>
+        <v>75.14649964542305</v>
       </c>
       <c r="C10" s="21" t="n">
-        <v>75.46543617594334</v>
+        <v>75.17136104115589</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>75.41355181444709</v>
+        <v>75.11971079906914</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>75.26334436582385</v>
+        <v>74.97018113616322</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>74.98453604724203</v>
+        <v>74.69263089298269</v>
       </c>
     </row>
     <row r="12">
@@ -3078,102 +3078,102 @@
     </row>
     <row r="14">
       <c r="A14" s="25" t="n">
-        <v>0.2459972623102014</v>
+        <v>0.2496011971672128</v>
       </c>
       <c r="B14" s="21" t="n">
-        <v>95.81066339046944</v>
+        <v>95.41176600476099</v>
       </c>
       <c r="C14" s="21" t="n">
-        <v>87.07426555586915</v>
+        <v>86.7171976381851</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>80.11950123398847</v>
+        <v>79.79571815341392</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>74.44887329779274</v>
+        <v>74.15221646814004</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>69.73436473180824</v>
+        <v>69.46024876336722</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="25" t="n">
-        <v>0.2609972623102014</v>
+        <v>0.2646011971672128</v>
       </c>
       <c r="B15" s="21" t="n">
-        <v>94.16702824626745</v>
+        <v>93.77856819235348</v>
       </c>
       <c r="C15" s="21" t="n">
-        <v>85.60291295914895</v>
+        <v>85.25514192298188</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>78.78523908241954</v>
+        <v>78.46984575199836</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>73.22633669819382</v>
+        <v>72.93733064911554</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>68.60466818819098</v>
+        <v>68.33758923250676</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="25" t="n">
-        <v>0.2759972623102014</v>
+        <v>0.2796011971672128</v>
       </c>
       <c r="B16" s="21" t="n">
-        <v>92.56625875258041</v>
+        <v>92.18787520046035</v>
       </c>
       <c r="C16" s="21" t="n">
-        <v>84.16974373134545</v>
+        <v>83.83094910546551</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>77.48543592414525</v>
+        <v>77.17814396333017</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>72.03522511570489</v>
+        <v>71.75360759839367</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>67.50387670994803</v>
+        <v>67.24359421349114</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="25" t="n">
-        <v>0.2909972623102015</v>
+        <v>0.2946011971672128</v>
       </c>
       <c r="B17" s="21" t="n">
-        <v>91.00687812172588</v>
+        <v>90.63822589638099</v>
       </c>
       <c r="C17" s="21" t="n">
-        <v>82.7734462215537</v>
+        <v>82.44332141283824</v>
       </c>
       <c r="D17" s="21" t="n">
-        <v>76.21891141503147</v>
+        <v>75.91944490895575</v>
       </c>
       <c r="E17" s="21" t="n">
-        <v>70.87446513112444</v>
+        <v>70.59998521268145</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>66.43100565040024</v>
+        <v>66.17728942131778</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="25" t="n">
-        <v>0.3059972623102014</v>
+        <v>0.3096011971672128</v>
       </c>
       <c r="B18" s="21" t="n">
-        <v>89.48747340545246</v>
+        <v>89.12822216389782</v>
       </c>
       <c r="C18" s="21" t="n">
-        <v>81.4127653738033</v>
+        <v>81.09101693857316</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>74.98453604724203</v>
+        <v>74.69263089298269</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>69.7430294737607</v>
+        <v>69.47544694443567</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>65.3851126208112</v>
+        <v>65.13774228675879</v>
       </c>
     </row>
     <row r="20">
@@ -3275,19 +3275,19 @@
         </is>
       </c>
       <c r="B26" s="21" t="n">
-        <v>66.31823154997149</v>
+        <v>66.05696993971418</v>
       </c>
       <c r="C26" s="21" t="n">
-        <v>71.90183373705834</v>
+        <v>71.61755695152216</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>77.48543592414525</v>
+        <v>77.17814396333017</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>83.06903811123212</v>
+        <v>82.73873097513817</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>88.652640298319</v>
+        <v>88.29931798694616</v>
       </c>
     </row>
     <row r="28">
@@ -3332,19 +3332,19 @@
         </is>
       </c>
       <c r="B30" s="21" t="n">
-        <v>73.48402150417607</v>
+        <v>73.17672954336101</v>
       </c>
       <c r="C30" s="21" t="n">
-        <v>75.48472871416067</v>
+        <v>75.17743675334559</v>
       </c>
       <c r="D30" s="21" t="n">
-        <v>77.48543592414525</v>
+        <v>77.17814396333017</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>79.48614313412983</v>
+        <v>79.17885117331475</v>
       </c>
       <c r="F30" s="21" t="n">
-        <v>81.48685034411442</v>
+        <v>81.17955838329934</v>
       </c>
     </row>
     <row r="32">
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="B17" s="43">
-        <f>Assumptions!$B$132/5.34</f>
+        <f>Assumptions!$B$134/5.34</f>
         <v/>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
         </is>
       </c>
       <c r="B20" s="8">
-        <f>Assumptions!$B$134/Assumptions!$B$135-1</f>
+        <f>Assumptions!$B$136/Assumptions!$B$137-1</f>
         <v/>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="B21" s="17">
-        <f>Assumptions!$B$56*Assumptions!$B$134/Assumptions!$B$135</f>
+        <f>Assumptions!$B$58*Assumptions!$B$136/Assumptions!$B$137</f>
         <v/>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="B24" s="8">
-        <f>Assumptions!$B$136/Assumptions!$B$134</f>
+        <f>Assumptions!$B$138/Assumptions!$B$136</f>
         <v/>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="B26" s="17">
-        <f>4*Assumptions!$B$137</f>
+        <f>4*Assumptions!$B$139</f>
         <v/>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="B29" s="17">
-        <f>Assumptions!$B$138-Assumptions!$B$139-Assumptions!$B$150</f>
+        <f>Assumptions!$B$140-Assumptions!$B$141-Assumptions!$B$152</f>
         <v/>
       </c>
     </row>
@@ -4030,11 +4030,11 @@
         </is>
       </c>
       <c r="B5" s="14">
-        <f>Assumptions!$B$56</f>
+        <f>Assumptions!$B$58</f>
         <v/>
       </c>
       <c r="C5" s="14">
-        <f>Assumptions!$B$77</f>
+        <f>Assumptions!$B$79</f>
         <v/>
       </c>
       <c r="D5" s="14">
@@ -4061,15 +4061,15 @@
         </is>
       </c>
       <c r="B6" s="14">
-        <f>Assumptions!$B$167</f>
+        <f>Assumptions!$B$169</f>
         <v/>
       </c>
       <c r="C6" s="14">
-        <f>Assumptions!$B$168</f>
+        <f>Assumptions!$B$170</f>
         <v/>
       </c>
       <c r="D6" s="14">
-        <f>Assumptions!$B$169</f>
+        <f>Assumptions!$B$171</f>
         <v/>
       </c>
       <c r="E6" s="40">
@@ -4092,15 +4092,15 @@
         </is>
       </c>
       <c r="B7" s="14">
-        <f>Assumptions!$B$170</f>
+        <f>Assumptions!$B$172</f>
         <v/>
       </c>
       <c r="C7" s="14">
-        <f>Assumptions!$B$171</f>
+        <f>Assumptions!$B$173</f>
         <v/>
       </c>
       <c r="D7" s="14">
-        <f>Assumptions!$B$172</f>
+        <f>Assumptions!$B$174</f>
         <v/>
       </c>
       <c r="E7" s="40">
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="B13" s="49">
-        <f>Assumptions!$B$160</f>
+        <f>Assumptions!$B$162</f>
         <v/>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
         </is>
       </c>
       <c r="B14" s="49">
-        <f>Assumptions!$B$161</f>
+        <f>Assumptions!$B$163</f>
         <v/>
       </c>
     </row>
@@ -4181,16 +4181,16 @@
         </is>
       </c>
       <c r="B15" s="49">
+        <f>Assumptions!$B$166</f>
+        <v/>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of which CEMENT exports (Mt)</t>
+        </is>
+      </c>
+      <c r="D15" s="19">
         <f>Assumptions!$B$164</f>
-        <v/>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  of which CEMENT exports (Mt)</t>
-        </is>
-      </c>
-      <c r="D15" s="19">
-        <f>Assumptions!$B$162</f>
         <v/>
       </c>
     </row>
@@ -4201,16 +4201,16 @@
         </is>
       </c>
       <c r="B16" s="49">
+        <f>Assumptions!$B$167</f>
+        <v/>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of which CLINKER exports (Mt) — no cement mill involved</t>
+        </is>
+      </c>
+      <c r="D16" s="19">
         <f>Assumptions!$B$165</f>
-        <v/>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  of which CLINKER exports (Mt) — no cement mill involved</t>
-        </is>
-      </c>
-      <c r="D16" s="19">
-        <f>Assumptions!$B$163</f>
         <v/>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="B17" s="49">
-        <f>Assumptions!$B$166</f>
+        <f>Assumptions!$B$168</f>
         <v/>
       </c>
       <c r="C17" t="inlineStr">
@@ -4597,15 +4597,15 @@
         </is>
       </c>
       <c r="B17" s="13">
-        <f>((Assumptions!$B$154-15)*Assumptions!$B$14*Assumptions!$B$12+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <f>((Assumptions!$B$156-15)*Assumptions!$B$14*Assumptions!$B$12+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
         <v/>
       </c>
       <c r="C17" s="13">
-        <f>(Assumptions!$B$154*Assumptions!$B$14*Assumptions!$B$12+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <f>(Assumptions!$B$156*Assumptions!$B$14*Assumptions!$B$12+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
         <v/>
       </c>
       <c r="D17" s="13">
-        <f>((Assumptions!$B$154+15)*Assumptions!$B$14*Assumptions!$B$12+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <f>((Assumptions!$B$156+15)*Assumptions!$B$14*Assumptions!$B$12+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
         <v/>
       </c>
       <c r="E17" s="8">
@@ -4620,15 +4620,15 @@
         </is>
       </c>
       <c r="B18" s="13">
-        <f>('Relative &amp; Normalized'!$B$12*(Assumptions!$B$156-1)+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <f>('Relative &amp; Normalized'!$B$12*(Assumptions!$B$158-1)+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
         <v/>
       </c>
       <c r="C18" s="13">
-        <f>('Relative &amp; Normalized'!$B$12*Assumptions!$B$156+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <f>('Relative &amp; Normalized'!$B$12*Assumptions!$B$158+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
         <v/>
       </c>
       <c r="D18" s="13">
-        <f>('Relative &amp; Normalized'!$B$12*(Assumptions!$B$156+1)+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
+        <f>('Relative &amp; Normalized'!$B$12*(Assumptions!$B$158+1)+DCF!$B$40+DCF!$B$41)/DCF!$B$43</f>
         <v/>
       </c>
       <c r="E18" s="8">
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="B6" s="17">
-        <f>Assumptions!$B$153</f>
+        <f>Assumptions!$B$155</f>
         <v/>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="B7" s="17">
-        <f>Assumptions!$B$154</f>
+        <f>Assumptions!$B$156</f>
         <v/>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="B14" s="19">
-        <f>(Assumptions!$B$5*DCF!$B$43-DCF!B40+Assumptions!$B$119)/Assumptions!$B$14/Assumptions!$B$12</f>
+        <f>(Assumptions!$B$5*DCF!$B$43-DCF!B40+Assumptions!$B$121)/Assumptions!$B$14/Assumptions!$B$12</f>
         <v/>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="B15" s="17">
-        <f>Assumptions!$B$107+Assumptions!$B$108</f>
+        <f>Assumptions!$B$109+Assumptions!$B$110</f>
         <v/>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
         <v/>
       </c>
       <c r="E20" s="21" t="n">
-        <v>77.62270984824453</v>
+        <v>77.31456564655174</v>
       </c>
       <c r="F20" s="8">
         <f>E20/D20-1</f>
@@ -4995,7 +4995,7 @@
         <v/>
       </c>
       <c r="E22" s="21" t="n">
-        <v>81.6305426255454</v>
+        <v>81.30994683832586</v>
       </c>
       <c r="F22" s="8">
         <f>E22/D22-1</f>
@@ -5023,7 +5023,7 @@
         <v/>
       </c>
       <c r="E23" s="21" t="n">
-        <v>94.92458818577515</v>
+        <v>94.53742109347019</v>
       </c>
       <c r="F23" s="8">
         <f>E23/D23-1</f>
@@ -5075,15 +5075,15 @@
         </is>
       </c>
       <c r="B28" s="14">
-        <f>Assumptions!$B$84</f>
+        <f>Assumptions!$B$86</f>
         <v/>
       </c>
       <c r="C28" s="14">
-        <f>Assumptions!$B$85</f>
+        <f>Assumptions!$B$87</f>
         <v/>
       </c>
       <c r="D28" s="14">
-        <f>Assumptions!$B$86</f>
+        <f>Assumptions!$B$88</f>
         <v/>
       </c>
     </row>
@@ -5113,15 +5113,15 @@
         </is>
       </c>
       <c r="B30" s="14">
-        <f>Assumptions!$B$81</f>
+        <f>Assumptions!$B$83</f>
         <v/>
       </c>
       <c r="C30" s="14">
-        <f>Assumptions!$B$82</f>
+        <f>Assumptions!$B$84</f>
         <v/>
       </c>
       <c r="D30" s="14">
-        <f>Assumptions!$B$83</f>
+        <f>Assumptions!$B$85</f>
         <v/>
       </c>
     </row>
@@ -5189,15 +5189,15 @@
         </is>
       </c>
       <c r="B34" s="8">
-        <f>B32/(Assumptions!$B$118+Assumptions!$B$126)</f>
+        <f>B32/(Assumptions!$B$120+Assumptions!$B$128)</f>
         <v/>
       </c>
       <c r="C34" s="8">
-        <f>C32/(Assumptions!$B$117+Assumptions!$B$125)</f>
+        <f>C32/(Assumptions!$B$119+Assumptions!$B$127)</f>
         <v/>
       </c>
       <c r="D34" s="8">
-        <f>D32/(Assumptions!$B$116+DCF!$C$44)</f>
+        <f>D32/(Assumptions!$B$118+DCF!$C$44)</f>
         <v/>
       </c>
     </row>
@@ -5291,7 +5291,7 @@
         </is>
       </c>
       <c r="B41" s="8">
-        <f>Assumptions!$B$51</f>
+        <f>Assumptions!$B$53</f>
         <v/>
       </c>
     </row>
@@ -5341,7 +5341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J175"/>
+  <dimension ref="A1:J177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="56" customWidth="1" min="1" max="1"/>
@@ -6067,7 +6067,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Equity risk premium</t>
+          <t>Equity risk premium, TOTAL (split into the two legs below)</t>
         </is>
       </c>
       <c r="B43" s="25" t="n">
@@ -6077,386 +6077,376 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Euribor (EBRD and NBE reference rate)</t>
+          <t xml:space="preserve">   of which the MATURE premium — beta applies to this leg only</t>
         </is>
       </c>
       <c r="B44" s="25" t="n">
-        <v>0.0249</v>
+        <v>0.04242</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EGP marginal borrowing rate (corridor + 0.6%)</t>
+          <t>Egypt country premium — charged FLAT, once, never multiplied by beta</t>
         </is>
       </c>
       <c r="B45" s="25" t="n">
-        <v>0.206</v>
+        <v>0.05168</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Expected EGP depreciation against the euro</t>
+          <t>Euribor (EBRD and NBE reference rate)</t>
         </is>
       </c>
       <c r="B46" s="25" t="n">
-        <v>0.06</v>
+        <v>0.0249</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Terminal cost of debt</t>
+          <t>EGP marginal borrowing rate (corridor + 0.6%)</t>
         </is>
       </c>
       <c r="B47" s="25" t="n">
-        <v>0.15</v>
+        <v>0.206</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Terminal risk-free rate</t>
+          <t>Expected EGP depreciation against the euro</t>
         </is>
       </c>
       <c r="B48" s="25" t="n">
-        <v>0.105</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Terminal equity risk premium</t>
+          <t>Terminal cost of debt</t>
         </is>
       </c>
       <c r="B49" s="25" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Terminal debt weight</t>
-        </is>
-      </c>
-      <c r="B50" s="24" t="n">
-        <v>0.2</v>
+          <t>Terminal risk-free rate</t>
+        </is>
+      </c>
+      <c r="B50" s="25" t="n">
+        <v>0.105</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Terminal growth rate</t>
-        </is>
-      </c>
-      <c r="B51" s="24" t="n">
-        <v>0.07000000000000006</v>
+          <t>Terminal equity risk premium</t>
+        </is>
+      </c>
+      <c r="B51" s="25" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Elapsed fraction of FY2026 at the valuation date</t>
-        </is>
-      </c>
-      <c r="B52" s="26" t="n">
-        <v>0.5</v>
+          <t>Terminal debt weight</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t>AUDITED INCOME STATEMENT — PASTED CLASS 1 (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B53" s="15" t="n"/>
-      <c r="C53" s="15" t="n"/>
-      <c r="D53" s="15" t="n"/>
-      <c r="E53" s="15" t="n"/>
-      <c r="F53" s="15" t="n"/>
-      <c r="G53" s="15" t="n"/>
-      <c r="H53" s="15" t="n"/>
-      <c r="I53" s="15" t="n"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Terminal growth rate</t>
+        </is>
+      </c>
+      <c r="B53" s="24" t="n">
+        <v>0.07000000000000006</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FY2023 sales (net)</t>
-        </is>
-      </c>
-      <c r="B54" s="30" t="n">
-        <v>6042.831338</v>
+          <t>Elapsed fraction of FY2026 at the valuation date</t>
+        </is>
+      </c>
+      <c r="B54" s="26" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>FY2024 sales (net)</t>
-        </is>
-      </c>
-      <c r="B55" s="30" t="n">
-        <v>8729.782821000001</v>
-      </c>
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>AUDITED INCOME STATEMENT — PASTED CLASS 1 (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="n"/>
+      <c r="C55" s="15" t="n"/>
+      <c r="D55" s="15" t="n"/>
+      <c r="E55" s="15" t="n"/>
+      <c r="F55" s="15" t="n"/>
+      <c r="G55" s="15" t="n"/>
+      <c r="H55" s="15" t="n"/>
+      <c r="I55" s="15" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FY2025 sales (net)</t>
+          <t>FY2023 sales (net)</t>
         </is>
       </c>
       <c r="B56" s="30" t="n">
-        <v>12447.320081</v>
+        <v>6042.831338</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FY2023 cost of sales</t>
+          <t>FY2024 sales (net)</t>
         </is>
       </c>
       <c r="B57" s="30" t="n">
-        <v>4759.815212</v>
+        <v>8729.782821000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FY2024 cost of sales</t>
+          <t>FY2025 sales (net)</t>
         </is>
       </c>
       <c r="B58" s="30" t="n">
-        <v>6642.972487</v>
+        <v>12447.320081</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FY2025 cost of sales</t>
+          <t>FY2023 cost of sales</t>
         </is>
       </c>
       <c r="B59" s="30" t="n">
-        <v>7389.054416</v>
+        <v>4759.815212</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FY2023 general and administrative expenses</t>
+          <t>FY2024 cost of sales</t>
         </is>
       </c>
       <c r="B60" s="30" t="n">
-        <v>183.940276</v>
+        <v>6642.972487</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FY2024 general and administrative expenses</t>
+          <t>FY2025 cost of sales</t>
         </is>
       </c>
       <c r="B61" s="30" t="n">
-        <v>267.798104</v>
+        <v>7389.054416</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FY2025 general and administrative expenses</t>
+          <t>FY2023 general and administrative expenses</t>
         </is>
       </c>
       <c r="B62" s="30" t="n">
-        <v>384.332833</v>
+        <v>183.940276</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FY2023 provisions charged</t>
+          <t>FY2024 general and administrative expenses</t>
         </is>
       </c>
       <c r="B63" s="30" t="n">
-        <v>15.220195</v>
+        <v>267.798104</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FY2024 provisions charged</t>
+          <t>FY2025 general and administrative expenses</t>
         </is>
       </c>
       <c r="B64" s="30" t="n">
-        <v>56.05295</v>
+        <v>384.332833</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FY2025 provisions charged</t>
+          <t>FY2023 provisions charged</t>
         </is>
       </c>
       <c r="B65" s="30" t="n">
-        <v>74.505707</v>
+        <v>15.220195</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FY2023 expected credit losses</t>
+          <t>FY2024 provisions charged</t>
         </is>
       </c>
       <c r="B66" s="30" t="n">
-        <v>4.745753</v>
+        <v>56.05295</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FY2024 expected credit losses</t>
+          <t>FY2025 provisions charged</t>
         </is>
       </c>
       <c r="B67" s="30" t="n">
-        <v>-1.106452</v>
+        <v>74.505707</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FY2025 expected credit losses</t>
+          <t>FY2023 expected credit losses</t>
         </is>
       </c>
       <c r="B68" s="30" t="n">
-        <v>3.603563</v>
+        <v>4.745753</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FY2023 profit before tax</t>
+          <t>FY2024 expected credit losses</t>
         </is>
       </c>
       <c r="B69" s="30" t="n">
-        <v>930.231432</v>
+        <v>-1.106452</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FY2024 profit before tax</t>
+          <t>FY2025 expected credit losses</t>
         </is>
       </c>
       <c r="B70" s="30" t="n">
-        <v>1505.866118</v>
+        <v>3.603563</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FY2025 profit before tax</t>
+          <t>FY2023 profit before tax</t>
         </is>
       </c>
       <c r="B71" s="30" t="n">
-        <v>4725.157878</v>
+        <v>930.231432</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FY2023 income tax</t>
+          <t>FY2024 profit before tax</t>
         </is>
       </c>
       <c r="B72" s="30" t="n">
-        <v>232.732802</v>
+        <v>1505.866118</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FY2024 income tax</t>
+          <t>FY2025 profit before tax</t>
         </is>
       </c>
       <c r="B73" s="30" t="n">
-        <v>345.730996</v>
+        <v>4725.157878</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FY2025 income tax</t>
+          <t>FY2023 income tax</t>
         </is>
       </c>
       <c r="B74" s="30" t="n">
-        <v>1125.467657</v>
+        <v>232.732802</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FY2023 attributable profit</t>
+          <t>FY2024 income tax</t>
         </is>
       </c>
       <c r="B75" s="30" t="n">
-        <v>697.488741</v>
+        <v>345.730996</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FY2024 attributable profit</t>
+          <t>FY2025 income tax</t>
         </is>
       </c>
       <c r="B76" s="30" t="n">
-        <v>1160.129411</v>
+        <v>1125.467657</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FY2025 attributable profit</t>
+          <t>FY2023 attributable profit</t>
         </is>
       </c>
       <c r="B77" s="30" t="n">
-        <v>3599.585937</v>
+        <v>697.488741</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FY2023 earnings per share</t>
-        </is>
-      </c>
-      <c r="B78" s="21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
+          <t>FY2024 attributable profit</t>
+        </is>
+      </c>
+      <c r="B78" s="30" t="n">
+        <v>1160.129411</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FY2024 earnings per share</t>
-        </is>
-      </c>
-      <c r="B79" s="21" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
+          <t>FY2025 attributable profit</t>
+        </is>
+      </c>
+      <c r="B79" s="30" t="n">
+        <v>3599.585937</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FY2025 earnings per share</t>
+          <t>FY2023 earnings per share</t>
         </is>
       </c>
       <c r="B80" s="21" t="n">
-        <v>9.49</v>
+        <v>1.81</v>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
@@ -6467,871 +6457,871 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FY2023 depreciation and amortisation</t>
-        </is>
-      </c>
-      <c r="B81" s="30" t="n">
-        <v>250.424521</v>
+          <t>FY2024 earnings per share</t>
+        </is>
+      </c>
+      <c r="B81" s="21" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>FY2024 depreciation and amortisation</t>
-        </is>
-      </c>
-      <c r="B82" s="30" t="n">
-        <v>256.801527</v>
+          <t>FY2025 earnings per share</t>
+        </is>
+      </c>
+      <c r="B82" s="21" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FY2025 depreciation and amortisation</t>
+          <t>FY2023 depreciation and amortisation</t>
         </is>
       </c>
       <c r="B83" s="30" t="n">
-        <v>289.771295</v>
+        <v>250.424521</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FY2023 capital expenditure</t>
+          <t>FY2024 depreciation and amortisation</t>
         </is>
       </c>
       <c r="B84" s="30" t="n">
-        <v>58.543963</v>
+        <v>256.801527</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FY2024 capital expenditure</t>
+          <t>FY2025 depreciation and amortisation</t>
         </is>
       </c>
       <c r="B85" s="30" t="n">
-        <v>912.0154</v>
+        <v>289.771295</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FY2025 capital expenditure</t>
+          <t>FY2023 capital expenditure</t>
         </is>
       </c>
       <c r="B86" s="30" t="n">
-        <v>796.47076</v>
+        <v>58.543963</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FY2025 interest income</t>
+          <t>FY2024 capital expenditure</t>
         </is>
       </c>
       <c r="B87" s="30" t="n">
-        <v>226.274781</v>
+        <v>912.0154</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FY2025 other income</t>
+          <t>FY2025 capital expenditure</t>
         </is>
       </c>
       <c r="B88" s="30" t="n">
-        <v>53.339508</v>
+        <v>796.47076</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FY2025 finance costs</t>
+          <t>FY2025 interest income</t>
         </is>
       </c>
       <c r="B89" s="30" t="n">
-        <v>49.841733</v>
+        <v>226.274781</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FY2025 foreign exchange differences</t>
+          <t>FY2025 other income</t>
         </is>
       </c>
       <c r="B90" s="30" t="n">
-        <v>-101.57824</v>
+        <v>53.339508</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="15" t="inlineStr">
-        <is>
-          <t>AUDITED REVENUE AND COST NOTES (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B91" s="15" t="n"/>
-      <c r="C91" s="15" t="n"/>
-      <c r="D91" s="15" t="n"/>
-      <c r="E91" s="15" t="n"/>
-      <c r="F91" s="15" t="n"/>
-      <c r="G91" s="15" t="n"/>
-      <c r="H91" s="15" t="n"/>
-      <c r="I91" s="15" t="n"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>FY2025 finance costs</t>
+        </is>
+      </c>
+      <c r="B91" s="30" t="n">
+        <v>49.841733</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>FY2025 local sales of goods</t>
+          <t>FY2025 foreign exchange differences</t>
         </is>
       </c>
       <c r="B92" s="30" t="n">
-        <v>8350.454610000001</v>
+        <v>-101.57824</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>FY2025 local services</t>
-        </is>
-      </c>
-      <c r="B93" s="30" t="n">
-        <v>281.863546</v>
-      </c>
+      <c r="A93" s="15" t="inlineStr">
+        <is>
+          <t>AUDITED REVENUE AND COST NOTES (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B93" s="15" t="n"/>
+      <c r="C93" s="15" t="n"/>
+      <c r="D93" s="15" t="n"/>
+      <c r="E93" s="15" t="n"/>
+      <c r="F93" s="15" t="n"/>
+      <c r="G93" s="15" t="n"/>
+      <c r="H93" s="15" t="n"/>
+      <c r="I93" s="15" t="n"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FY2025 export sales of goods</t>
+          <t>FY2025 local sales of goods</t>
         </is>
       </c>
       <c r="B94" s="30" t="n">
-        <v>3356.422381</v>
+        <v>8350.454610000001</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>FY2025 export services</t>
+          <t>FY2025 local services</t>
         </is>
       </c>
       <c r="B95" s="30" t="n">
-        <v>458.579544</v>
+        <v>281.863546</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FY2024 total local sales</t>
+          <t>FY2025 export sales of goods</t>
         </is>
       </c>
       <c r="B96" s="30" t="n">
-        <v>4883.304477</v>
+        <v>3356.422381</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FY2024 total export sales</t>
+          <t>FY2025 export services</t>
         </is>
       </c>
       <c r="B97" s="30" t="n">
-        <v>3846.478344</v>
+        <v>458.579544</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>FY2025 cost of sales — materials and fuel</t>
+          <t>FY2024 total local sales</t>
         </is>
       </c>
       <c r="B98" s="30" t="n">
-        <v>5698.184715</v>
+        <v>4883.304477</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>FY2025 cost of sales — transportation</t>
+          <t>FY2024 total export sales</t>
         </is>
       </c>
       <c r="B99" s="30" t="n">
-        <v>764.279332</v>
+        <v>3846.478344</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FY2025 cost of sales — overheads</t>
+          <t>FY2025 cost of sales — materials and fuel</t>
         </is>
       </c>
       <c r="B100" s="30" t="n">
-        <v>641.143208</v>
+        <v>5698.184715</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FY2025 administrative depreciation</t>
+          <t>FY2025 cost of sales — transportation</t>
         </is>
       </c>
       <c r="B101" s="30" t="n">
-        <v>4.324134</v>
+        <v>764.279332</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="15" t="inlineStr">
-        <is>
-          <t>AUDITED BALANCE SHEET — PASTED CLASS 1 (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B102" s="15" t="n"/>
-      <c r="C102" s="15" t="n"/>
-      <c r="D102" s="15" t="n"/>
-      <c r="E102" s="15" t="n"/>
-      <c r="F102" s="15" t="n"/>
-      <c r="G102" s="15" t="n"/>
-      <c r="H102" s="15" t="n"/>
-      <c r="I102" s="15" t="n"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>FY2025 cost of sales — overheads</t>
+        </is>
+      </c>
+      <c r="B102" s="30" t="n">
+        <v>641.143208</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Total assets FY2025</t>
+          <t>FY2025 administrative depreciation</t>
         </is>
       </c>
       <c r="B103" s="30" t="n">
-        <v>8783.721849</v>
+        <v>4.324134</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Total assets FY2024</t>
-        </is>
-      </c>
-      <c r="B104" s="30" t="n">
-        <v>5848.616103</v>
-      </c>
+      <c r="A104" s="15" t="inlineStr">
+        <is>
+          <t>AUDITED BALANCE SHEET — PASTED CLASS 1 (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B104" s="15" t="n"/>
+      <c r="C104" s="15" t="n"/>
+      <c r="D104" s="15" t="n"/>
+      <c r="E104" s="15" t="n"/>
+      <c r="F104" s="15" t="n"/>
+      <c r="G104" s="15" t="n"/>
+      <c r="H104" s="15" t="n"/>
+      <c r="I104" s="15" t="n"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Total assets FY2023</t>
+          <t>Total assets FY2025</t>
         </is>
       </c>
       <c r="B105" s="30" t="n">
-        <v>3887.527427</v>
+        <v>8783.721849</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Total liabilities FY2025</t>
+          <t>Total assets FY2024</t>
         </is>
       </c>
       <c r="B106" s="30" t="n">
-        <v>4140.989609</v>
+        <v>5848.616103</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Property, plant and equipment FY2025</t>
+          <t>Total assets FY2023</t>
         </is>
       </c>
       <c r="B107" s="30" t="n">
-        <v>2522.323523</v>
+        <v>3887.527427</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Assets under construction FY2025</t>
+          <t>Total liabilities FY2025</t>
         </is>
       </c>
       <c r="B108" s="30" t="n">
-        <v>391.543753</v>
+        <v>4140.989609</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Intangible assets FY2025</t>
+          <t>Property, plant and equipment FY2025</t>
         </is>
       </c>
       <c r="B109" s="30" t="n">
-        <v>106.799617</v>
+        <v>2522.323523</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Inventories FY2025</t>
+          <t>Assets under construction FY2025</t>
         </is>
       </c>
       <c r="B110" s="30" t="n">
-        <v>1053.646218</v>
+        <v>391.543753</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Trade receivables FY2025</t>
+          <t>Intangible assets FY2025</t>
         </is>
       </c>
       <c r="B111" s="30" t="n">
-        <v>244.416417</v>
+        <v>106.799617</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Debtors and other debit balances FY2025</t>
+          <t>Inventories FY2025</t>
         </is>
       </c>
       <c r="B112" s="30" t="n">
-        <v>1004.779062</v>
+        <v>1053.646218</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Cash and bank balances FY2025</t>
+          <t>Trade receivables FY2025</t>
         </is>
       </c>
       <c r="B113" s="30" t="n">
-        <v>3459.391229</v>
+        <v>244.416417</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Cash and bank balances FY2024</t>
+          <t>Debtors and other debit balances FY2025</t>
         </is>
       </c>
       <c r="B114" s="30" t="n">
-        <v>1687.062873</v>
+        <v>1004.779062</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Cash and bank balances FY2023</t>
+          <t>Cash and bank balances FY2025</t>
         </is>
       </c>
       <c r="B115" s="30" t="n">
-        <v>561.09968</v>
+        <v>3459.391229</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Equity attributable to owners FY2025</t>
+          <t>Cash and bank balances FY2024</t>
         </is>
       </c>
       <c r="B116" s="30" t="n">
-        <v>4642.574235</v>
+        <v>1687.062873</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Equity attributable to owners FY2024</t>
+          <t>Cash and bank balances FY2023</t>
         </is>
       </c>
       <c r="B117" s="30" t="n">
-        <v>2303.472299</v>
+        <v>561.09968</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Equity attributable to owners FY2023</t>
+          <t>Equity attributable to owners FY2025</t>
         </is>
       </c>
       <c r="B118" s="30" t="n">
-        <v>1754.221659</v>
+        <v>4642.574235</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Non-controlling interests FY2025</t>
-        </is>
-      </c>
-      <c r="B119" s="23" t="n">
-        <v>0.158005</v>
+          <t>Equity attributable to owners FY2024</t>
+        </is>
+      </c>
+      <c r="B119" s="30" t="n">
+        <v>2303.472299</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="15" t="inlineStr">
-        <is>
-          <t>AUDITED DEBT NOTE 25 (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B120" s="15" t="n"/>
-      <c r="C120" s="15" t="n"/>
-      <c r="D120" s="15" t="n"/>
-      <c r="E120" s="15" t="n"/>
-      <c r="F120" s="15" t="n"/>
-      <c r="G120" s="15" t="n"/>
-      <c r="H120" s="15" t="n"/>
-      <c r="I120" s="15" t="n"/>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Equity attributable to owners FY2023</t>
+        </is>
+      </c>
+      <c r="B120" s="30" t="n">
+        <v>1754.221659</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CIB credit facilities — EGP</t>
-        </is>
-      </c>
-      <c r="B121" s="30" t="n">
-        <v>99.916937</v>
+          <t>Non-controlling interests FY2025</t>
+        </is>
+      </c>
+      <c r="B121" s="23" t="n">
+        <v>0.158005</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>National Bank of Egypt facility — EUR</t>
-        </is>
-      </c>
-      <c r="B122" s="30" t="n">
-        <v>145.741484</v>
-      </c>
+      <c r="A122" s="15" t="inlineStr">
+        <is>
+          <t>AUDITED DEBT NOTE 25 (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B122" s="15" t="n"/>
+      <c r="C122" s="15" t="n"/>
+      <c r="D122" s="15" t="n"/>
+      <c r="E122" s="15" t="n"/>
+      <c r="F122" s="15" t="n"/>
+      <c r="G122" s="15" t="n"/>
+      <c r="H122" s="15" t="n"/>
+      <c r="I122" s="15" t="n"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EBRD facility — EUR</t>
+          <t>CIB credit facilities — EGP</t>
         </is>
       </c>
       <c r="B123" s="30" t="n">
-        <v>888.274195</v>
+        <v>99.916937</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Lease liabilities</t>
+          <t>National Bank of Egypt facility — EUR</t>
         </is>
       </c>
       <c r="B124" s="30" t="n">
-        <v>1.176042</v>
+        <v>145.741484</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Total interest-bearing debt FY2024</t>
+          <t>EBRD facility — EUR</t>
         </is>
       </c>
       <c r="B125" s="30" t="n">
-        <v>760.917684</v>
+        <v>888.274195</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Total interest-bearing debt FY2023</t>
+          <t>Lease liabilities</t>
         </is>
       </c>
       <c r="B126" s="30" t="n">
-        <v>90.07427300000001</v>
+        <v>1.176042</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>FY2025 loan interest expense</t>
+          <t>Total interest-bearing debt FY2024</t>
         </is>
       </c>
       <c r="B127" s="30" t="n">
-        <v>24.61313</v>
+        <v>760.917684</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FY2025 credit-facility interest expense</t>
+          <t>Total interest-bearing debt FY2023</t>
         </is>
       </c>
       <c r="B128" s="30" t="n">
-        <v>23.00737</v>
+        <v>90.07427300000001</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>FY2024 loan interest expense</t>
+          <t>FY2025 loan interest expense</t>
         </is>
       </c>
       <c r="B129" s="30" t="n">
-        <v>2.754107</v>
+        <v>24.61313</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>FY2024 credit-facility interest expense</t>
+          <t>FY2025 credit-facility interest expense</t>
         </is>
       </c>
       <c r="B130" s="30" t="n">
-        <v>85.95302599999999</v>
+        <v>23.00737</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="15" t="inlineStr">
-        <is>
-          <t>DIVIDENDS AND Q1-2026 (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B131" s="15" t="n"/>
-      <c r="C131" s="15" t="n"/>
-      <c r="D131" s="15" t="n"/>
-      <c r="E131" s="15" t="n"/>
-      <c r="F131" s="15" t="n"/>
-      <c r="G131" s="15" t="n"/>
-      <c r="H131" s="15" t="n"/>
-      <c r="I131" s="15" t="n"/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>FY2024 loan interest expense</t>
+        </is>
+      </c>
+      <c r="B131" s="30" t="n">
+        <v>2.754107</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>FY2025 dividend declared</t>
+          <t>FY2024 credit-facility interest expense</t>
         </is>
       </c>
       <c r="B132" s="30" t="n">
-        <v>2001.79216</v>
+        <v>85.95302599999999</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>FY2024 dividend approved and paid</t>
-        </is>
-      </c>
-      <c r="B133" s="30" t="n">
-        <v>1102.110289</v>
-      </c>
+      <c r="A133" s="15" t="inlineStr">
+        <is>
+          <t>DIVIDENDS AND Q1-2026 (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B133" s="15" t="n"/>
+      <c r="C133" s="15" t="n"/>
+      <c r="D133" s="15" t="n"/>
+      <c r="E133" s="15" t="n"/>
+      <c r="F133" s="15" t="n"/>
+      <c r="G133" s="15" t="n"/>
+      <c r="H133" s="15" t="n"/>
+      <c r="I133" s="15" t="n"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Q1-2026 sales</t>
+          <t>FY2025 dividend declared</t>
         </is>
       </c>
       <c r="B134" s="30" t="n">
-        <v>2995.95935</v>
+        <v>2001.79216</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Q1-2025 sales</t>
+          <t>FY2024 dividend approved and paid</t>
         </is>
       </c>
       <c r="B135" s="30" t="n">
-        <v>2554.448091</v>
+        <v>1102.110289</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Q1-2026 gross profit</t>
+          <t>Q1-2026 sales</t>
         </is>
       </c>
       <c r="B136" s="30" t="n">
-        <v>1286.145881</v>
+        <v>2995.95935</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Q1-2026 attributable profit</t>
+          <t>Q1-2025 sales</t>
         </is>
       </c>
       <c r="B137" s="30" t="n">
-        <v>943.068309</v>
+        <v>2554.448091</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Q1-2026 cash and bank balances</t>
+          <t>Q1-2026 gross profit</t>
         </is>
       </c>
       <c r="B138" s="30" t="n">
-        <v>4379.627379</v>
+        <v>1286.145881</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Q1-2026 interest-bearing debt</t>
+          <t>Q1-2026 attributable profit</t>
         </is>
       </c>
       <c r="B139" s="30" t="n">
-        <v>1260.509089</v>
+        <v>943.068309</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Cash and bank balances, reviewed 30 June 2026</t>
+          <t>Q1-2026 cash and bank balances</t>
         </is>
       </c>
       <c r="B140" s="30" t="n">
-        <v>1970.50114</v>
+        <v>4379.627379</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Interest-bearing debt, reviewed 30 June 2026</t>
+          <t>Q1-2026 interest-bearing debt</t>
         </is>
       </c>
       <c r="B141" s="30" t="n">
-        <v>1283.288394</v>
+        <v>1260.509089</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Non-controlling interests, reviewed 30 June 2026</t>
-        </is>
-      </c>
-      <c r="B142" s="23" t="n">
-        <v>0.216054</v>
+          <t>Cash and bank balances, reviewed 30 June 2026</t>
+        </is>
+      </c>
+      <c r="B142" s="30" t="n">
+        <v>1970.50114</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FY2026+ local price calibration on the H1-2026 reviewed half</t>
-        </is>
-      </c>
-      <c r="B143" s="23" t="n">
-        <v>1.078760449086537</v>
+          <t>Interest-bearing debt, reviewed 30 June 2026</t>
+        </is>
+      </c>
+      <c r="B143" s="30" t="n">
+        <v>1283.288394</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FY2026+ export price calibration on the H1-2026 reviewed half</t>
+          <t>Non-controlling interests, reviewed 30 June 2026</t>
         </is>
       </c>
       <c r="B144" s="23" t="n">
-        <v>0.8711327338803936</v>
+        <v>0.216054</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FY2026+ cash-cost calibration on the SAME half</t>
+          <t>FY2026+ local price calibration on the H1-2026 reviewed half</t>
         </is>
       </c>
       <c r="B145" s="23" t="n">
-        <v>0.9763641792055924</v>
+        <v>1.078760449086537</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Services as a share of goods revenue, recalibrated on the half</t>
+          <t>FY2026+ export price calibration on the H1-2026 reviewed half</t>
         </is>
       </c>
       <c r="B146" s="23" t="n">
-        <v>0.0442178203915956</v>
+        <v>0.8711327338803936</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Depreciation correction from this name's own fundamental walk-forward</t>
+          <t>FY2026+ cash-cost calibration on the SAME half</t>
         </is>
       </c>
       <c r="B147" s="23" t="n">
-        <v>1.0298</v>
+        <v>0.9763641792055924</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Export subsidy as a share of export revenue, FY2025 DISCLOSED rate</t>
+          <t>Services as a share of goods revenue, recalibrated on the half</t>
         </is>
       </c>
       <c r="B148" s="23" t="n">
-        <v>0.008556374712707386</v>
+        <v>0.0442178203915956</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Other income excluding the export subsidy, FY2025</t>
-        </is>
-      </c>
-      <c r="B149" s="26" t="n">
-        <v>20.696922</v>
+          <t>Depreciation correction from this name's own fundamental walk-forward</t>
+        </is>
+      </c>
+      <c r="B149" s="23" t="n">
+        <v>1.0298</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Q1-2026 dividends payable</t>
-        </is>
-      </c>
-      <c r="B150" s="30" t="n">
-        <v>2001.79216</v>
+          <t>Export subsidy as a share of export revenue, FY2025 DISCLOSED rate</t>
+        </is>
+      </c>
+      <c r="B150" s="23" t="n">
+        <v>0.008556374712707386</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Q1-2026 finance costs</t>
-        </is>
-      </c>
-      <c r="B151" s="30" t="n">
-        <v>11.168843</v>
+          <t>Other income excluding the export subsidy, FY2025</t>
+        </is>
+      </c>
+      <c r="B151" s="26" t="n">
+        <v>20.696922</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="15" t="inlineStr">
-        <is>
-          <t>LENS INPUTS</t>
-        </is>
-      </c>
-      <c r="B152" s="15" t="n"/>
-      <c r="C152" s="15" t="n"/>
-      <c r="D152" s="15" t="n"/>
-      <c r="E152" s="15" t="n"/>
-      <c r="F152" s="15" t="n"/>
-      <c r="G152" s="15" t="n"/>
-      <c r="H152" s="15" t="n"/>
-      <c r="I152" s="15" t="n"/>
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Q1-2026 dividends payable</t>
+        </is>
+      </c>
+      <c r="B152" s="30" t="n">
+        <v>2001.79216</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Replacement cost per annual tonne</t>
+          <t>Q1-2026 finance costs</t>
         </is>
       </c>
       <c r="B153" s="30" t="n">
-        <v>130</v>
-      </c>
-      <c r="C153" s="5" t="inlineStr">
-        <is>
-          <t>USD/t</t>
-        </is>
+        <v>11.168843</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Justified enterprise value per annual tonne</t>
-        </is>
-      </c>
-      <c r="B154" s="30" t="n">
-        <v>95</v>
-      </c>
-      <c r="C154" s="5" t="inlineStr">
-        <is>
-          <t>USD/t</t>
-        </is>
-      </c>
+      <c r="A154" s="15" t="inlineStr">
+        <is>
+          <t>LENS INPUTS</t>
+        </is>
+      </c>
+      <c r="B154" s="15" t="n"/>
+      <c r="C154" s="15" t="n"/>
+      <c r="D154" s="15" t="n"/>
+      <c r="E154" s="15" t="n"/>
+      <c r="F154" s="15" t="n"/>
+      <c r="G154" s="15" t="n"/>
+      <c r="H154" s="15" t="n"/>
+      <c r="I154" s="15" t="n"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Justified EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="B155" s="31" t="n">
-        <v>4.5</v>
+          <t>Replacement cost per annual tonne</t>
+        </is>
+      </c>
+      <c r="B155" s="30" t="n">
+        <v>130</v>
+      </c>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>USD/t</t>
+        </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Justified price/earnings</t>
-        </is>
-      </c>
-      <c r="B156" s="31" t="n">
-        <v>7</v>
+          <t>Justified enterprise value per annual tonne</t>
+        </is>
+      </c>
+      <c r="B156" s="30" t="n">
+        <v>95</v>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>USD/t</t>
+        </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Mid-cycle EBITDA margin</t>
-        </is>
-      </c>
-      <c r="B157" s="24" t="n">
-        <v>0.312</v>
+          <t>Justified EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B157" s="31" t="n">
+        <v>4.5</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Normalised revenue haircut</t>
-        </is>
-      </c>
-      <c r="B158" s="24" t="n">
-        <v>0.9399999999999999</v>
+          <t>Justified price/earnings</t>
+        </is>
+      </c>
+      <c r="B158" s="31" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="15" t="inlineStr">
-        <is>
-          <t>SECTOR AND PEERS</t>
-        </is>
-      </c>
-      <c r="B159" s="15" t="n"/>
-      <c r="C159" s="15" t="n"/>
-      <c r="D159" s="15" t="n"/>
-      <c r="E159" s="15" t="n"/>
-      <c r="F159" s="15" t="n"/>
-      <c r="G159" s="15" t="n"/>
-      <c r="H159" s="15" t="n"/>
-      <c r="I159" s="15" t="n"/>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Mid-cycle EBITDA margin</t>
+        </is>
+      </c>
+      <c r="B159" s="24" t="n">
+        <v>0.312</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Egyptian nameplate capacity</t>
-        </is>
-      </c>
-      <c r="B160" s="28" t="n">
-        <v>76</v>
-      </c>
-      <c r="C160" s="5" t="inlineStr">
-        <is>
-          <t>Mt</t>
-        </is>
+          <t>Normalised revenue haircut</t>
+        </is>
+      </c>
+      <c r="B160" s="24" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Egyptian sales 2025 — cement AND clinker</t>
-        </is>
-      </c>
-      <c r="B161" s="28" t="n">
-        <v>72.62479999999999</v>
-      </c>
-      <c r="C161" s="5" t="inlineStr">
-        <is>
-          <t>Mt</t>
-        </is>
-      </c>
+      <c r="A161" s="15" t="inlineStr">
+        <is>
+          <t>SECTOR AND PEERS</t>
+        </is>
+      </c>
+      <c r="B161" s="15" t="n"/>
+      <c r="C161" s="15" t="n"/>
+      <c r="D161" s="15" t="n"/>
+      <c r="E161" s="15" t="n"/>
+      <c r="F161" s="15" t="n"/>
+      <c r="G161" s="15" t="n"/>
+      <c r="H161" s="15" t="n"/>
+      <c r="I161" s="15" t="n"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">  of which cement exports</t>
+          <t>Egyptian nameplate capacity</t>
         </is>
       </c>
       <c r="B162" s="28" t="n">
-        <v>11.063</v>
+        <v>76</v>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
@@ -7342,26 +7332,26 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">  of which clinker exports</t>
+          <t>Egyptian sales 2025 — cement AND clinker</t>
         </is>
       </c>
       <c r="B163" s="28" t="n">
-        <v>7.5689</v>
+        <v>72.62479999999999</v>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>Mt — leaves at the kiln, so it is OUT of the cement utilisation ratio</t>
+          <t>Mt</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Egyptian consumption 2025</t>
+          <t xml:space="preserve">  of which cement exports</t>
         </is>
       </c>
       <c r="B164" s="28" t="n">
-        <v>53.9929</v>
+        <v>11.063</v>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
@@ -7372,26 +7362,26 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Egyptian exports 2025</t>
+          <t xml:space="preserve">  of which clinker exports</t>
         </is>
       </c>
       <c r="B165" s="28" t="n">
-        <v>18.6319</v>
+        <v>7.5689</v>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>Mt</t>
+          <t>Mt — leaves at the kiln, so it is OUT of the cement utilisation ratio</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Dormant capacity under revival</t>
+          <t>Egyptian consumption 2025</t>
         </is>
       </c>
       <c r="B166" s="28" t="n">
-        <v>12.6</v>
+        <v>53.9929</v>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
@@ -7402,72 +7392,102 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Peer — Sinai Cement revenue</t>
-        </is>
-      </c>
-      <c r="B167" s="30" t="n">
-        <v>9090</v>
+          <t>Egyptian exports 2025</t>
+        </is>
+      </c>
+      <c r="B167" s="28" t="n">
+        <v>18.6319</v>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Peer — Sinai Cement profit</t>
-        </is>
-      </c>
-      <c r="B168" s="30" t="n">
-        <v>2290</v>
+          <t>Dormant capacity under revival</t>
+        </is>
+      </c>
+      <c r="B168" s="28" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>Mt</t>
+        </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Peer — Sinai Cement market capitalisation</t>
+          <t>Peer — Sinai Cement revenue</t>
         </is>
       </c>
       <c r="B169" s="30" t="n">
-        <v>20604.19</v>
+        <v>9090</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Peer — Misr Beni Suef revenue</t>
+          <t>Peer — Sinai Cement profit</t>
         </is>
       </c>
       <c r="B170" s="30" t="n">
-        <v>5700</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Peer — Misr Beni Suef profit</t>
+          <t>Peer — Sinai Cement market capitalisation</t>
         </is>
       </c>
       <c r="B171" s="30" t="n">
-        <v>3946</v>
+        <v>20604.19</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
+          <t>Peer — Misr Beni Suef revenue</t>
+        </is>
+      </c>
+      <c r="B172" s="30" t="n">
+        <v>5700</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Peer — Misr Beni Suef profit</t>
+        </is>
+      </c>
+      <c r="B173" s="30" t="n">
+        <v>3946</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
           <t>Peer — Misr Beni Suef market capitalisation</t>
         </is>
       </c>
-      <c r="B172" s="30" t="n">
+      <c r="B174" s="30" t="n">
         <v>13730</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="5" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="5" t="inlineStr">
         <is>
           <t>Every cell on this sheet is BLUE — an input. Nothing here is computed from anything else here.</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="5" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
         <is>
           <t>Everything on every other sheet that can be derived from these is a formula.</t>
         </is>
@@ -7475,8 +7495,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A175:J175"/>
-    <mergeCell ref="A174:J174"/>
+    <mergeCell ref="A177:J177"/>
+    <mergeCell ref="A176:J176"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7948,7 +7968,7 @@
         </is>
       </c>
       <c r="B21" s="14">
-        <f>Assumptions!$B$92</f>
+        <f>Assumptions!$B$94</f>
         <v/>
       </c>
     </row>
@@ -7970,7 +7990,7 @@
         </is>
       </c>
       <c r="B23" s="14">
-        <f>Assumptions!$B$94</f>
+        <f>Assumptions!$B$96</f>
         <v/>
       </c>
     </row>
@@ -8063,7 +8083,7 @@
         </is>
       </c>
       <c r="B31" s="14">
-        <f>Assumptions!$B$98</f>
+        <f>Assumptions!$B$100</f>
         <v/>
       </c>
     </row>
@@ -8074,7 +8094,7 @@
         </is>
       </c>
       <c r="B32" s="14">
-        <f>Assumptions!$B$99</f>
+        <f>Assumptions!$B$101</f>
         <v/>
       </c>
     </row>
@@ -8085,7 +8105,7 @@
         </is>
       </c>
       <c r="B33" s="17">
-        <f>Assumptions!$B$100+Assumptions!$B$62-Assumptions!$B$101</f>
+        <f>Assumptions!$B$102+Assumptions!$B$64-Assumptions!$B$103</f>
         <v/>
       </c>
     </row>
@@ -8559,23 +8579,23 @@
         <v/>
       </c>
       <c r="C56" s="17">
-        <f>$B$22*Assumptions!$C$27*Assumptions!$B$143</f>
+        <f>$B$22*Assumptions!$C$27*Assumptions!$B$145</f>
         <v/>
       </c>
       <c r="D56" s="17">
-        <f>$B$22*Assumptions!$D$27*Assumptions!$B$143</f>
+        <f>$B$22*Assumptions!$D$27*Assumptions!$B$145</f>
         <v/>
       </c>
       <c r="E56" s="17">
-        <f>$B$22*Assumptions!$E$27*Assumptions!$B$143</f>
+        <f>$B$22*Assumptions!$E$27*Assumptions!$B$145</f>
         <v/>
       </c>
       <c r="F56" s="17">
-        <f>$B$22*Assumptions!$F$27*Assumptions!$B$143</f>
+        <f>$B$22*Assumptions!$F$27*Assumptions!$B$145</f>
         <v/>
       </c>
       <c r="G56" s="17">
-        <f>$B$22*Assumptions!$G$27*Assumptions!$B$143</f>
+        <f>$B$22*Assumptions!$G$27*Assumptions!$B$145</f>
         <v/>
       </c>
     </row>
@@ -8590,23 +8610,23 @@
         <v/>
       </c>
       <c r="C57" s="17">
-        <f>$B$26*Assumptions!$C$28*Assumptions!$C$29*Assumptions!$B$144</f>
+        <f>$B$26*Assumptions!$C$28*Assumptions!$C$29*Assumptions!$B$146</f>
         <v/>
       </c>
       <c r="D57" s="17">
-        <f>$B$26*Assumptions!$D$28*Assumptions!$D$29*Assumptions!$B$144</f>
+        <f>$B$26*Assumptions!$D$28*Assumptions!$D$29*Assumptions!$B$146</f>
         <v/>
       </c>
       <c r="E57" s="17">
-        <f>$B$26*Assumptions!$E$28*Assumptions!$E$29*Assumptions!$B$144</f>
+        <f>$B$26*Assumptions!$E$28*Assumptions!$E$29*Assumptions!$B$146</f>
         <v/>
       </c>
       <c r="F57" s="17">
-        <f>$B$26*Assumptions!$F$28*Assumptions!$F$29*Assumptions!$B$144</f>
+        <f>$B$26*Assumptions!$F$28*Assumptions!$F$29*Assumptions!$B$146</f>
         <v/>
       </c>
       <c r="G57" s="17">
-        <f>$B$26*Assumptions!$G$28*Assumptions!$G$29*Assumptions!$B$144</f>
+        <f>$B$26*Assumptions!$G$28*Assumptions!$G$29*Assumptions!$B$146</f>
         <v/>
       </c>
     </row>
@@ -8776,23 +8796,23 @@
         <v/>
       </c>
       <c r="C63" s="37">
-        <f>C62*(1+Assumptions!$B$146)</f>
+        <f>C62*(1+Assumptions!$B$148)</f>
         <v/>
       </c>
       <c r="D63" s="37">
-        <f>D62*(1+Assumptions!$B$146)</f>
+        <f>D62*(1+Assumptions!$B$148)</f>
         <v/>
       </c>
       <c r="E63" s="37">
-        <f>E62*(1+Assumptions!$B$146)</f>
+        <f>E62*(1+Assumptions!$B$148)</f>
         <v/>
       </c>
       <c r="F63" s="37">
-        <f>F62*(1+Assumptions!$B$146)</f>
+        <f>F62*(1+Assumptions!$B$148)</f>
         <v/>
       </c>
       <c r="G63" s="37">
-        <f>G62*(1+Assumptions!$B$146)</f>
+        <f>G62*(1+Assumptions!$B$148)</f>
         <v/>
       </c>
     </row>
@@ -8838,23 +8858,23 @@
         <v/>
       </c>
       <c r="C65" s="17">
-        <f>$B$35*Assumptions!$C$30*(1-Assumptions!$C$31)*C46*Assumptions!$B$145</f>
+        <f>$B$35*Assumptions!$C$30*(1-Assumptions!$C$31)*C46*Assumptions!$B$147</f>
         <v/>
       </c>
       <c r="D65" s="17">
-        <f>$B$35*Assumptions!$D$30*(1-Assumptions!$D$31)*D46*Assumptions!$B$145</f>
+        <f>$B$35*Assumptions!$D$30*(1-Assumptions!$D$31)*D46*Assumptions!$B$147</f>
         <v/>
       </c>
       <c r="E65" s="17">
-        <f>$B$35*Assumptions!$E$30*(1-Assumptions!$E$31)*E46*Assumptions!$B$145</f>
+        <f>$B$35*Assumptions!$E$30*(1-Assumptions!$E$31)*E46*Assumptions!$B$147</f>
         <v/>
       </c>
       <c r="F65" s="17">
-        <f>$B$35*Assumptions!$F$30*(1-Assumptions!$F$31)*F46*Assumptions!$B$145</f>
+        <f>$B$35*Assumptions!$F$30*(1-Assumptions!$F$31)*F46*Assumptions!$B$147</f>
         <v/>
       </c>
       <c r="G65" s="17">
-        <f>$B$35*Assumptions!$G$30*(1-Assumptions!$G$31)*G46*Assumptions!$B$145</f>
+        <f>$B$35*Assumptions!$G$30*(1-Assumptions!$G$31)*G46*Assumptions!$B$147</f>
         <v/>
       </c>
     </row>
@@ -8869,23 +8889,23 @@
         <v/>
       </c>
       <c r="C66" s="17">
-        <f>$B$36*Assumptions!$C$30*C55*Assumptions!$B$145</f>
+        <f>$B$36*Assumptions!$C$30*C55*Assumptions!$B$147</f>
         <v/>
       </c>
       <c r="D66" s="17">
-        <f>$B$36*Assumptions!$D$30*D55*Assumptions!$B$145</f>
+        <f>$B$36*Assumptions!$D$30*D55*Assumptions!$B$147</f>
         <v/>
       </c>
       <c r="E66" s="17">
-        <f>$B$36*Assumptions!$E$30*E55*Assumptions!$B$145</f>
+        <f>$B$36*Assumptions!$E$30*E55*Assumptions!$B$147</f>
         <v/>
       </c>
       <c r="F66" s="17">
-        <f>$B$36*Assumptions!$F$30*F55*Assumptions!$B$145</f>
+        <f>$B$36*Assumptions!$F$30*F55*Assumptions!$B$147</f>
         <v/>
       </c>
       <c r="G66" s="17">
-        <f>$B$36*Assumptions!$G$30*G55*Assumptions!$B$145</f>
+        <f>$B$36*Assumptions!$G$30*G55*Assumptions!$B$147</f>
         <v/>
       </c>
     </row>
@@ -8900,23 +8920,23 @@
         <v/>
       </c>
       <c r="C67" s="17">
-        <f>$B$37*Assumptions!$C$30*C55*Assumptions!$B$145</f>
+        <f>$B$37*Assumptions!$C$30*C55*Assumptions!$B$147</f>
         <v/>
       </c>
       <c r="D67" s="17">
-        <f>$B$37*Assumptions!$D$30*D55*Assumptions!$B$145</f>
+        <f>$B$37*Assumptions!$D$30*D55*Assumptions!$B$147</f>
         <v/>
       </c>
       <c r="E67" s="17">
-        <f>$B$37*Assumptions!$E$30*E55*Assumptions!$B$145</f>
+        <f>$B$37*Assumptions!$E$30*E55*Assumptions!$B$147</f>
         <v/>
       </c>
       <c r="F67" s="17">
-        <f>$B$37*Assumptions!$F$30*F55*Assumptions!$B$145</f>
+        <f>$B$37*Assumptions!$F$30*F55*Assumptions!$B$147</f>
         <v/>
       </c>
       <c r="G67" s="17">
-        <f>$B$37*Assumptions!$G$30*G55*Assumptions!$B$145</f>
+        <f>$B$37*Assumptions!$G$30*G55*Assumptions!$B$147</f>
         <v/>
       </c>
     </row>
@@ -8989,27 +9009,27 @@
         </is>
       </c>
       <c r="B70" s="17">
-        <f>(Assumptions!$B$65+Assumptions!$B$68)/Assumptions!$B$56*B63</f>
+        <f>(Assumptions!$B$67+Assumptions!$B$70)/Assumptions!$B$58*B63</f>
         <v/>
       </c>
       <c r="C70" s="17">
-        <f>(Assumptions!$B$65+Assumptions!$B$68)/Assumptions!$B$56*C63</f>
+        <f>(Assumptions!$B$67+Assumptions!$B$70)/Assumptions!$B$58*C63</f>
         <v/>
       </c>
       <c r="D70" s="17">
-        <f>(Assumptions!$B$65+Assumptions!$B$68)/Assumptions!$B$56*D63</f>
+        <f>(Assumptions!$B$67+Assumptions!$B$70)/Assumptions!$B$58*D63</f>
         <v/>
       </c>
       <c r="E70" s="17">
-        <f>(Assumptions!$B$65+Assumptions!$B$68)/Assumptions!$B$56*E63</f>
+        <f>(Assumptions!$B$67+Assumptions!$B$70)/Assumptions!$B$58*E63</f>
         <v/>
       </c>
       <c r="F70" s="17">
-        <f>(Assumptions!$B$65+Assumptions!$B$68)/Assumptions!$B$56*F63</f>
+        <f>(Assumptions!$B$67+Assumptions!$B$70)/Assumptions!$B$58*F63</f>
         <v/>
       </c>
       <c r="G70" s="17">
-        <f>(Assumptions!$B$65+Assumptions!$B$68)/Assumptions!$B$56*G63</f>
+        <f>(Assumptions!$B$67+Assumptions!$B$70)/Assumptions!$B$58*G63</f>
         <v/>
       </c>
     </row>
@@ -9189,7 +9209,7 @@
         </is>
       </c>
       <c r="B77" s="14">
-        <f>Assumptions!$B$56</f>
+        <f>Assumptions!$B$58</f>
         <v/>
       </c>
     </row>
@@ -9497,7 +9517,7 @@
         </is>
       </c>
       <c r="B5" s="17">
-        <f>Assumptions!$B$56</f>
+        <f>Assumptions!$B$58</f>
         <v/>
       </c>
     </row>
@@ -9508,7 +9528,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <f>Assumptions!$B$158</f>
+        <f>Assumptions!$B$160</f>
         <v/>
       </c>
     </row>
@@ -9530,7 +9550,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>Assumptions!$B$157</f>
+        <f>Assumptions!$B$159</f>
         <v/>
       </c>
     </row>
@@ -9552,7 +9572,7 @@
         </is>
       </c>
       <c r="B10" s="17">
-        <f>-Assumptions!$B$83</f>
+        <f>-Assumptions!$B$85</f>
         <v/>
       </c>
     </row>
@@ -9631,7 +9651,7 @@
         </is>
       </c>
       <c r="B18" s="40">
-        <f>Assumptions!$B$155</f>
+        <f>Assumptions!$B$157</f>
         <v/>
       </c>
     </row>
@@ -9710,7 +9730,7 @@
         </is>
       </c>
       <c r="B26" s="40">
-        <f>Assumptions!$B$156</f>
+        <f>Assumptions!$B$158</f>
         <v/>
       </c>
     </row>
@@ -9940,23 +9960,23 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>B5*Assumptions!$B$34*Assumptions!$B$147</f>
+        <f>B5*Assumptions!$B$34*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>C5*Assumptions!$C$34*Assumptions!$B$147</f>
+        <f>C5*Assumptions!$C$34*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>D5*Assumptions!$D$34*Assumptions!$B$147</f>
+        <f>D5*Assumptions!$D$34*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>E5*Assumptions!$E$34*Assumptions!$B$147</f>
+        <f>E5*Assumptions!$E$34*Assumptions!$B$149</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>F5*Assumptions!$F$34*Assumptions!$B$147</f>
+        <f>F5*Assumptions!$F$34*Assumptions!$B$149</f>
         <v/>
       </c>
     </row>
@@ -9967,23 +9987,23 @@
         </is>
       </c>
       <c r="B9" s="17">
-        <f>B7-B8+Assumptions!$B$148*'Segments'!C60+Assumptions!$B$148*'Segments'!C61+Assumptions!$B$149*Assumptions!$C$30</f>
+        <f>B7-B8+Assumptions!$B$150*'Segments'!C60+Assumptions!$B$150*'Segments'!C61+Assumptions!$B$151*Assumptions!$C$30</f>
         <v/>
       </c>
       <c r="C9" s="17">
-        <f>C7-C8+Assumptions!$B$148*'Segments'!D60+Assumptions!$B$148*'Segments'!D61+Assumptions!$B$149*Assumptions!$D$30</f>
+        <f>C7-C8+Assumptions!$B$150*'Segments'!D60+Assumptions!$B$150*'Segments'!D61+Assumptions!$B$151*Assumptions!$D$30</f>
         <v/>
       </c>
       <c r="D9" s="17">
-        <f>D7-D8+Assumptions!$B$148*'Segments'!E60+Assumptions!$B$148*'Segments'!E61+Assumptions!$B$149*Assumptions!$E$30</f>
+        <f>D7-D8+Assumptions!$B$150*'Segments'!E60+Assumptions!$B$150*'Segments'!E61+Assumptions!$B$151*Assumptions!$E$30</f>
         <v/>
       </c>
       <c r="E9" s="17">
-        <f>E7-E8+Assumptions!$B$148*'Segments'!F60+Assumptions!$B$148*'Segments'!F61+Assumptions!$B$149*Assumptions!$F$30</f>
+        <f>E7-E8+Assumptions!$B$150*'Segments'!F60+Assumptions!$B$150*'Segments'!F61+Assumptions!$B$151*Assumptions!$F$30</f>
         <v/>
       </c>
       <c r="F9" s="17">
-        <f>F7-F8+Assumptions!$B$148*'Segments'!G60+Assumptions!$B$148*'Segments'!G61+Assumptions!$B$149*Assumptions!$G$30</f>
+        <f>F7-F8+Assumptions!$B$150*'Segments'!G60+Assumptions!$B$150*'Segments'!G61+Assumptions!$B$151*Assumptions!$G$30</f>
         <v/>
       </c>
     </row>
@@ -10102,7 +10122,7 @@
         </is>
       </c>
       <c r="B14" s="17">
-        <f>-(B5-Assumptions!$B$56)*Assumptions!$B$38</f>
+        <f>-(B5-Assumptions!$B$58)*Assumptions!$B$38</f>
         <v/>
       </c>
       <c r="C14" s="17">
@@ -10129,7 +10149,7 @@
         </is>
       </c>
       <c r="B15" s="37">
-        <f>(B11+B12+B13+B14)*(1-Assumptions!$B$52)</f>
+        <f>(B11+B12+B13+B14)*(1-Assumptions!$B$54)</f>
         <v/>
       </c>
       <c r="C15" s="37">
@@ -10210,23 +10230,23 @@
         </is>
       </c>
       <c r="B18" s="41">
-        <f>1/(1+B17)^((1-Assumptions!$B$52)/2)</f>
+        <f>1/(1+B17)^((1-Assumptions!$B$54)/2)</f>
         <v/>
       </c>
       <c r="C18" s="41">
-        <f>1/((1+B17)^(1-Assumptions!$B$52)*(1+C17)^0.5)</f>
+        <f>1/((1+B17)^(1-Assumptions!$B$54)*(1+C17)^0.5)</f>
         <v/>
       </c>
       <c r="D18" s="41">
-        <f>1/((1+B17)^(1-Assumptions!$B$52)*(1+C17)*(1+D17)^0.5)</f>
+        <f>1/((1+B17)^(1-Assumptions!$B$54)*(1+C17)*(1+D17)^0.5)</f>
         <v/>
       </c>
       <c r="E18" s="41">
-        <f>1/((1+B17)^(1-Assumptions!$B$52)*(1+C17)*(1+D17)*(1+E17)^0.5)</f>
+        <f>1/((1+B17)^(1-Assumptions!$B$54)*(1+C17)*(1+D17)*(1+E17)^0.5)</f>
         <v/>
       </c>
       <c r="F18" s="41">
-        <f>1/((1+B17)^(1-Assumptions!$B$52)*(1+C17)*(1+D17)*(1+E17)*(1+F17)^0.5)</f>
+        <f>1/((1+B17)^(1-Assumptions!$B$54)*(1+C17)*(1+D17)*(1+E17)*(1+F17)^0.5)</f>
         <v/>
       </c>
     </row>
@@ -10278,7 +10298,7 @@
         </is>
       </c>
       <c r="B22" s="17">
-        <f>Assumptions!$B$14*Assumptions!$B$153*Assumptions!$B$12*Assumptions!$G$30/Assumptions!$C$30</f>
+        <f>Assumptions!$B$14*Assumptions!$B$155*Assumptions!$B$12*Assumptions!$G$30/Assumptions!$C$30</f>
         <v/>
       </c>
       <c r="C22" t="inlineStr">
@@ -10298,7 +10318,7 @@
         </is>
       </c>
       <c r="B23" s="17">
-        <f>F11*(1+Assumptions!$B$51)</f>
+        <f>F11*(1+Assumptions!$B$53)</f>
         <v/>
       </c>
       <c r="C23" t="inlineStr">
@@ -10327,7 +10347,7 @@
         </is>
       </c>
       <c r="D24" s="17">
-        <f>Assumptions!$B$51*F5*0.12284576</f>
+        <f>Assumptions!$B$53*F5*0.12284576</f>
         <v/>
       </c>
     </row>
@@ -10338,7 +10358,7 @@
         </is>
       </c>
       <c r="B25" s="8">
-        <f>('Income Statement'!D12*(1-Assumptions!$B$9))/(Assumptions!$B$116+$C$44)</f>
+        <f>('Income Statement'!D12*(1-Assumptions!$B$9))/(Assumptions!$B$118+$C$44)</f>
         <v/>
       </c>
       <c r="C25" t="inlineStr">
@@ -10347,7 +10367,7 @@
         </is>
       </c>
       <c r="D25" s="17">
-        <f>((1+Assumptions!$B$51)/(1+0.07000000)-1)*B22</f>
+        <f>((1+Assumptions!$B$53)/(1+0.07000000)-1)*B22</f>
         <v/>
       </c>
     </row>
@@ -10358,7 +10378,7 @@
         </is>
       </c>
       <c r="B26" s="8">
-        <f>Assumptions!$B$51/B24</f>
+        <f>Assumptions!$B$53/B24</f>
         <v/>
       </c>
       <c r="C26" t="inlineStr">
@@ -10378,7 +10398,7 @@
         </is>
       </c>
       <c r="B27" s="17">
-        <f>D26*(1+Assumptions!$B$51)/($C$50-Assumptions!$B$51)</f>
+        <f>D26*(1+Assumptions!$B$53)/($C$50-Assumptions!$B$53)</f>
         <v/>
       </c>
       <c r="C27" t="inlineStr">
@@ -10387,7 +10407,7 @@
         </is>
       </c>
       <c r="D27" s="8">
-        <f>B23/(1+Assumptions!$B$51)/B22</f>
+        <f>B23/(1+Assumptions!$B$53)/B22</f>
         <v/>
       </c>
     </row>
@@ -10409,7 +10429,7 @@
         </is>
       </c>
       <c r="B29" s="41">
-        <f>1/((1+B17)^(1-Assumptions!$B$52)*(1+C17)*(1+D17)*(1+E17)*(1+F17))</f>
+        <f>1/((1+B17)^(1-Assumptions!$B$54)*(1+C17)*(1+D17)*(1+E17)*(1+F17))</f>
         <v/>
       </c>
     </row>
@@ -10478,7 +10498,7 @@
         </is>
       </c>
       <c r="B35" s="17">
-        <f>Assumptions!$B$140</f>
+        <f>Assumptions!$B$142</f>
         <v/>
       </c>
       <c r="E35" t="inlineStr">
@@ -10494,7 +10514,7 @@
         </is>
       </c>
       <c r="B36" s="17">
-        <f>Assumptions!$B$113+B15/(1-Assumptions!$B$52)*Assumptions!$B$52+Assumptions!$B$113*Assumptions!$B$36*Assumptions!$B$52*(1-Assumptions!$B$9)-Assumptions!$B$132</f>
+        <f>Assumptions!$B$115+B15/(1-Assumptions!$B$54)*Assumptions!$B$54+Assumptions!$B$115*Assumptions!$B$36*Assumptions!$B$54*(1-Assumptions!$B$9)-Assumptions!$B$134</f>
         <v/>
       </c>
       <c r="C36" s="42">
@@ -10514,7 +10534,7 @@
         </is>
       </c>
       <c r="B37" s="43">
-        <f>(B36-Assumptions!$B$139-B38-B39)/B43</f>
+        <f>(B36-Assumptions!$B$141-B38-B39)/B43</f>
         <v/>
       </c>
       <c r="C37" s="42">
@@ -10534,7 +10554,7 @@
         </is>
       </c>
       <c r="B38" s="17">
-        <f>Assumptions!$B$140</f>
+        <f>Assumptions!$B$142</f>
         <v/>
       </c>
       <c r="C38" s="42">
@@ -10554,16 +10574,16 @@
         </is>
       </c>
       <c r="B39" s="17">
-        <f>-Assumptions!$B$141</f>
+        <f>-Assumptions!$B$143</f>
         <v/>
       </c>
       <c r="C39" s="42">
-        <f>C38+Assumptions!$B$10*Assumptions!$B$43</f>
+        <f>C38+Assumptions!$B$10*Assumptions!$B$44+Assumptions!$B$45</f>
         <v/>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cost of equity  (rf* + beta × premium)</t>
+          <t>Cost of equity  (rf* + beta × MATURE premium + country premium, flat)</t>
         </is>
       </c>
     </row>
@@ -10594,11 +10614,11 @@
         </is>
       </c>
       <c r="B41" s="43">
-        <f>-Assumptions!$B$142</f>
+        <f>-Assumptions!$B$144</f>
         <v/>
       </c>
       <c r="C41" s="44">
-        <f>(Assumptions!$B$121*Assumptions!$B$45+Assumptions!$B$122*(Assumptions!$B$44+0.03+Assumptions!$B$46)+Assumptions!$B$123*(Assumptions!$B$44+0.0435+Assumptions!$B$46)+Assumptions!$B$124*Assumptions!$B$45)/C44</f>
+        <f>(Assumptions!$B$123*Assumptions!$B$47+Assumptions!$B$124*(Assumptions!$B$46+0.03+Assumptions!$B$48)+Assumptions!$B$125*(Assumptions!$B$46+0.0435+Assumptions!$B$48)+Assumptions!$B$126*Assumptions!$B$47)/C44</f>
         <v/>
       </c>
       <c r="E41" t="inlineStr">
@@ -10658,7 +10678,7 @@
         <v/>
       </c>
       <c r="C44" s="17">
-        <f>Assumptions!$B$121+Assumptions!$B$122+Assumptions!$B$123+Assumptions!$B$124</f>
+        <f>Assumptions!$B$123+Assumptions!$B$124+Assumptions!$B$125+Assumptions!$B$126</f>
         <v/>
       </c>
       <c r="E44" t="inlineStr">
@@ -10680,7 +10700,7 @@
     </row>
     <row r="46">
       <c r="C46" s="8">
-        <f>(Assumptions!$B$122+Assumptions!$B$123)/C44</f>
+        <f>(Assumptions!$B$124+Assumptions!$B$125)/C44</f>
         <v/>
       </c>
       <c r="E46" t="inlineStr">
@@ -10691,7 +10711,7 @@
     </row>
     <row r="47">
       <c r="C47" s="34">
-        <f>Assumptions!$B$10/(1+(1-Assumptions!$B$8)*C43/(1-C43))*(1+(1-Assumptions!$B$8)*Assumptions!$B$50/(1-Assumptions!$B$50))</f>
+        <f>Assumptions!$B$10/(1+(1-Assumptions!$B$8)*C43/(1-C43))*(1+(1-Assumptions!$B$8)*Assumptions!$B$52/(1-Assumptions!$B$52))</f>
         <v/>
       </c>
       <c r="E47" t="inlineStr">
@@ -10702,7 +10722,7 @@
     </row>
     <row r="48">
       <c r="C48" s="42">
-        <f>Assumptions!$B$48+C47*Assumptions!$B$49</f>
+        <f>Assumptions!$B$50+C47*Assumptions!$B$51</f>
         <v/>
       </c>
       <c r="E48" t="inlineStr">
@@ -10713,7 +10733,7 @@
     </row>
     <row r="49">
       <c r="C49" s="42">
-        <f>Assumptions!$B$47*(1-Assumptions!$B$8)</f>
+        <f>Assumptions!$B$49*(1-Assumptions!$B$8)</f>
         <v/>
       </c>
       <c r="E49" t="inlineStr">
@@ -10724,7 +10744,7 @@
     </row>
     <row r="50">
       <c r="C50" s="44">
-        <f>(1-Assumptions!$B$50)*C48+Assumptions!$B$50*C49</f>
+        <f>(1-Assumptions!$B$52)*C48+Assumptions!$B$52*C49</f>
         <v/>
       </c>
       <c r="E50" t="inlineStr">
@@ -10787,7 +10807,7 @@
         </is>
       </c>
       <c r="B56" s="42">
-        <f>Assumptions!$B$45</f>
+        <f>Assumptions!$B$47</f>
         <v/>
       </c>
     </row>
@@ -10798,7 +10818,7 @@
         </is>
       </c>
       <c r="B57" s="42">
-        <f>Assumptions!$B$44+0.03</f>
+        <f>Assumptions!$B$46+0.03</f>
         <v/>
       </c>
     </row>
@@ -10809,7 +10829,7 @@
         </is>
       </c>
       <c r="B58" s="42">
-        <f>Assumptions!$B$44+0.0435</f>
+        <f>Assumptions!$B$46+0.0435</f>
         <v/>
       </c>
     </row>
@@ -10831,7 +10851,7 @@
         </is>
       </c>
       <c r="B60" s="42">
-        <f>(Assumptions!$B$129+Assumptions!$B$130)/((Assumptions!$B$126+Assumptions!$B$125)/2)</f>
+        <f>(Assumptions!$B$131+Assumptions!$B$132)/((Assumptions!$B$128+Assumptions!$B$127)/2)</f>
         <v/>
       </c>
     </row>
@@ -10842,7 +10862,7 @@
         </is>
       </c>
       <c r="B61" s="42">
-        <f>(Assumptions!$B$127+Assumptions!$B$128)/((Assumptions!$B$125+C44-Assumptions!$B$124)/2)</f>
+        <f>(Assumptions!$B$129+Assumptions!$B$130)/((Assumptions!$B$127+C44-Assumptions!$B$126)/2)</f>
         <v/>
       </c>
     </row>
@@ -10853,7 +10873,7 @@
         </is>
       </c>
       <c r="B62" s="42">
-        <f>Assumptions!$B$151*4/((C44+Assumptions!$B$139)/2)</f>
+        <f>Assumptions!$B$153*4/((C44+Assumptions!$B$141)/2)</f>
         <v/>
       </c>
     </row>
@@ -10864,7 +10884,7 @@
         </is>
       </c>
       <c r="B63" s="44">
-        <f>(Assumptions!$B$121*Assumptions!$B$45+Assumptions!$B$122*(Assumptions!$B$44+0.03+Assumptions!$B$46)+Assumptions!$B$123*(Assumptions!$B$44+0.0435+Assumptions!$B$46)+Assumptions!$B$124*Assumptions!$B$45)/C44</f>
+        <f>(Assumptions!$B$123*Assumptions!$B$47+Assumptions!$B$124*(Assumptions!$B$46+0.03+Assumptions!$B$48)+Assumptions!$B$125*(Assumptions!$B$46+0.0435+Assumptions!$B$48)+Assumptions!$B$126*Assumptions!$B$47)/C44</f>
         <v/>
       </c>
     </row>
@@ -11017,15 +11037,15 @@
         </is>
       </c>
       <c r="B5" s="14">
-        <f>Assumptions!$B$54</f>
+        <f>Assumptions!$B$56</f>
         <v/>
       </c>
       <c r="C5" s="14">
-        <f>Assumptions!$B$55</f>
+        <f>Assumptions!$B$57</f>
         <v/>
       </c>
       <c r="D5" s="14">
-        <f>Assumptions!$B$56</f>
+        <f>Assumptions!$B$58</f>
         <v/>
       </c>
       <c r="E5" s="14">
@@ -11056,15 +11076,15 @@
         </is>
       </c>
       <c r="B6" s="14">
-        <f>-Assumptions!$B$57</f>
+        <f>-Assumptions!$B$59</f>
         <v/>
       </c>
       <c r="C6" s="14">
-        <f>-Assumptions!$B$58</f>
+        <f>-Assumptions!$B$60</f>
         <v/>
       </c>
       <c r="D6" s="14">
-        <f>-Assumptions!$B$59</f>
+        <f>-Assumptions!$B$61</f>
         <v/>
       </c>
       <c r="E6" s="17" t="n"/>
@@ -11118,15 +11138,15 @@
         </is>
       </c>
       <c r="B9" s="14">
-        <f>-Assumptions!$B$60</f>
+        <f>-Assumptions!$B$62</f>
         <v/>
       </c>
       <c r="C9" s="14">
-        <f>-Assumptions!$B$61</f>
+        <f>-Assumptions!$B$63</f>
         <v/>
       </c>
       <c r="D9" s="14">
-        <f>-Assumptions!$B$62</f>
+        <f>-Assumptions!$B$64</f>
         <v/>
       </c>
     </row>
@@ -11137,15 +11157,15 @@
         </is>
       </c>
       <c r="B10" s="14">
-        <f>-Assumptions!$B$63-Assumptions!$B$66</f>
+        <f>-Assumptions!$B$65-Assumptions!$B$68</f>
         <v/>
       </c>
       <c r="C10" s="14">
-        <f>-Assumptions!$B$64-Assumptions!$B$67</f>
+        <f>-Assumptions!$B$66-Assumptions!$B$69</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>-Assumptions!$B$65-Assumptions!$B$68</f>
+        <f>-Assumptions!$B$67-Assumptions!$B$70</f>
         <v/>
       </c>
     </row>
@@ -11168,23 +11188,23 @@
         <v/>
       </c>
       <c r="E11" s="37">
-        <f>E14-E13+Assumptions!$B$148*'Segments'!C60+Assumptions!$B$148*'Segments'!C61+Assumptions!$B$149*Assumptions!$C$30</f>
+        <f>E14-E13+Assumptions!$B$150*'Segments'!C60+Assumptions!$B$150*'Segments'!C61+Assumptions!$B$151*Assumptions!$C$30</f>
         <v/>
       </c>
       <c r="F11" s="37">
-        <f>F14-F13+Assumptions!$B$148*'Segments'!D60+Assumptions!$B$148*'Segments'!D61+Assumptions!$B$149*Assumptions!$D$30</f>
+        <f>F14-F13+Assumptions!$B$150*'Segments'!D60+Assumptions!$B$150*'Segments'!D61+Assumptions!$B$151*Assumptions!$D$30</f>
         <v/>
       </c>
       <c r="G11" s="37">
-        <f>G14-G13+Assumptions!$B$148*'Segments'!E60+Assumptions!$B$148*'Segments'!E61+Assumptions!$B$149*Assumptions!$E$30</f>
+        <f>G14-G13+Assumptions!$B$150*'Segments'!E60+Assumptions!$B$150*'Segments'!E61+Assumptions!$B$151*Assumptions!$E$30</f>
         <v/>
       </c>
       <c r="H11" s="37">
-        <f>H14-H13+Assumptions!$B$148*'Segments'!F60+Assumptions!$B$148*'Segments'!F61+Assumptions!$B$149*Assumptions!$F$30</f>
+        <f>H14-H13+Assumptions!$B$150*'Segments'!F60+Assumptions!$B$150*'Segments'!F61+Assumptions!$B$151*Assumptions!$F$30</f>
         <v/>
       </c>
       <c r="I11" s="37">
-        <f>I14-I13+Assumptions!$B$148*'Segments'!G60+Assumptions!$B$148*'Segments'!G61+Assumptions!$B$149*Assumptions!$G$30</f>
+        <f>I14-I13+Assumptions!$B$150*'Segments'!G60+Assumptions!$B$150*'Segments'!G61+Assumptions!$B$151*Assumptions!$G$30</f>
         <v/>
       </c>
     </row>
@@ -11234,15 +11254,15 @@
         </is>
       </c>
       <c r="B13" s="14">
-        <f>Assumptions!$B$81</f>
+        <f>Assumptions!$B$83</f>
         <v/>
       </c>
       <c r="C13" s="14">
-        <f>Assumptions!$B$82</f>
+        <f>Assumptions!$B$84</f>
         <v/>
       </c>
       <c r="D13" s="14">
-        <f>Assumptions!$B$83</f>
+        <f>Assumptions!$B$85</f>
         <v/>
       </c>
       <c r="E13" s="14">
@@ -11351,35 +11371,35 @@
         </is>
       </c>
       <c r="B16" s="17">
-        <f>Assumptions!$B$69-B11</f>
+        <f>Assumptions!$B$71-B11</f>
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>Assumptions!$B$70-C11</f>
+        <f>Assumptions!$B$72-C11</f>
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>Assumptions!$B$87+Assumptions!$B$88-Assumptions!$B$89+Assumptions!$B$90+1.14</f>
+        <f>Assumptions!$B$89+Assumptions!$B$90-Assumptions!$B$91+Assumptions!$B$92+1.14</f>
         <v/>
       </c>
       <c r="E16" s="17">
-        <f>('Balance Sheet'!D9-Assumptions!$B$132)*Assumptions!$B$36-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$B$35-DCF!$C$44*DCF!$C$46*(Assumptions!$B$44+0.0435)</f>
+        <f>('Balance Sheet'!D9-Assumptions!$B$134)*Assumptions!$B$36-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$B$35-DCF!$C$44*DCF!$C$46*(Assumptions!$B$46+0.0435)</f>
         <v/>
       </c>
       <c r="F16" s="17">
-        <f>'Balance Sheet'!E9*Assumptions!$C$36-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$C$35-DCF!$C$44*DCF!$C$46*(Assumptions!$B$44+0.0435)</f>
+        <f>'Balance Sheet'!E9*Assumptions!$C$36-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$C$35-DCF!$C$44*DCF!$C$46*(Assumptions!$B$46+0.0435)</f>
         <v/>
       </c>
       <c r="G16" s="17">
-        <f>'Balance Sheet'!F9*Assumptions!$D$36-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$D$35-DCF!$C$44*DCF!$C$46*(Assumptions!$B$44+0.0435)</f>
+        <f>'Balance Sheet'!F9*Assumptions!$D$36-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$D$35-DCF!$C$44*DCF!$C$46*(Assumptions!$B$46+0.0435)</f>
         <v/>
       </c>
       <c r="H16" s="17">
-        <f>'Balance Sheet'!G9*Assumptions!$E$36-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$E$35-DCF!$C$44*DCF!$C$46*(Assumptions!$B$44+0.0435)</f>
+        <f>'Balance Sheet'!G9*Assumptions!$E$36-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$E$35-DCF!$C$44*DCF!$C$46*(Assumptions!$B$46+0.0435)</f>
         <v/>
       </c>
       <c r="I16" s="17">
-        <f>'Balance Sheet'!H9*Assumptions!$F$36-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$F$35-DCF!$C$44*DCF!$C$46*(Assumptions!$B$44+0.0435)</f>
+        <f>'Balance Sheet'!H9*Assumptions!$F$36-DCF!$C$44*(1-DCF!$C$46)*Assumptions!$F$35-DCF!$C$44*DCF!$C$46*(Assumptions!$B$46+0.0435)</f>
         <v/>
       </c>
     </row>
@@ -11390,15 +11410,15 @@
         </is>
       </c>
       <c r="B17" s="14">
-        <f>Assumptions!$B$69</f>
+        <f>Assumptions!$B$71</f>
         <v/>
       </c>
       <c r="C17" s="14">
-        <f>Assumptions!$B$70</f>
+        <f>Assumptions!$B$72</f>
         <v/>
       </c>
       <c r="D17" s="14">
-        <f>Assumptions!$B$71</f>
+        <f>Assumptions!$B$73</f>
         <v/>
       </c>
       <c r="E17" s="17">
@@ -11429,15 +11449,15 @@
         </is>
       </c>
       <c r="B18" s="14">
-        <f>-Assumptions!$B$72</f>
+        <f>-Assumptions!$B$74</f>
         <v/>
       </c>
       <c r="C18" s="14">
-        <f>-Assumptions!$B$73</f>
+        <f>-Assumptions!$B$75</f>
         <v/>
       </c>
       <c r="D18" s="14">
-        <f>-Assumptions!$B$74</f>
+        <f>-Assumptions!$B$76</f>
         <v/>
       </c>
       <c r="E18" s="17">
@@ -11507,15 +11527,15 @@
         </is>
       </c>
       <c r="B20" s="32">
-        <f>Assumptions!$B$75</f>
+        <f>Assumptions!$B$77</f>
         <v/>
       </c>
       <c r="C20" s="32">
-        <f>Assumptions!$B$76</f>
+        <f>Assumptions!$B$78</f>
         <v/>
       </c>
       <c r="D20" s="32">
-        <f>Assumptions!$B$77</f>
+        <f>Assumptions!$B$79</f>
         <v/>
       </c>
       <c r="E20" s="37">
@@ -11546,15 +11566,15 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>Assumptions!$B$78</f>
+        <f>Assumptions!$B$80</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>Assumptions!$B$79</f>
+        <f>Assumptions!$B$81</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>Assumptions!$B$80</f>
+        <f>Assumptions!$B$82</f>
         <v/>
       </c>
       <c r="E21" s="13">
@@ -11585,11 +11605,11 @@
         </is>
       </c>
       <c r="C22" s="14">
-        <f>Assumptions!$B$133</f>
+        <f>Assumptions!$B$135</f>
         <v/>
       </c>
       <c r="D22" s="14">
-        <f>Assumptions!$B$132</f>
+        <f>Assumptions!$B$134</f>
         <v/>
       </c>
       <c r="E22" s="17">
